--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903C265-0263-48E6-9BC4-12161A936C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5FE23E-CC30-41DB-A9A3-BE516EF4152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3465" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -4554,16 +4554,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4620,6 +4610,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5075,17 +5075,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
+      <c r="B3" s="32"/>
     </row>
     <row r="4" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="8" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="32"/>
     </row>
     <row r="10" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -5184,10 +5184,10 @@
     </row>
     <row r="17" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="13"/>
+      <c r="B18" s="32"/>
     </row>
     <row r="19" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -5291,19 +5291,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -5340,11 +5340,11 @@
     </row>
     <row r="7" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
     </row>
     <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5428,18 +5428,18 @@
     </row>
     <row r="19" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18855,342 +18855,342 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18" t="s">
+      <c r="B2" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15" t="s">
         <v>1220</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="16" t="s">
         <v>1221</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="17" t="s">
         <v>1222</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="22" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="18" t="s">
         <v>1223</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="19" t="s">
         <v>1224</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="20" t="s">
         <v>1225</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="22" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="18" t="s">
         <v>1226</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="19" t="s">
         <v>1227</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>1228</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="22" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="18" t="s">
         <v>1229</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="19" t="s">
         <v>1230</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="20" t="s">
         <v>1231</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="25" t="s">
+      <c r="B6" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="21" t="s">
         <v>1232</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="14" t="s">
         <v>1233</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>1234</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="22" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="18" t="s">
         <v>1235</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="19" t="s">
         <v>1236</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="14" t="s">
         <v>1237</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="22" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="18" t="s">
         <v>1238</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="19" t="s">
         <v>1239</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>1240</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="22" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="18" t="s">
         <v>1241</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="19" t="s">
         <v>1242</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>1243</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="22" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="18" t="s">
         <v>1244</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="19" t="s">
         <v>1245</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>1246</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="22" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="18" t="s">
         <v>1247</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="19" t="s">
         <v>1248</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>1249</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="22" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="18" t="s">
         <v>1250</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="19" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="17" t="s">
         <v>1252</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="22" t="s">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="18" t="s">
         <v>1253</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="19" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>1255</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="22" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="18" t="s">
         <v>1256</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="J14" s="19" t="s">
         <v>1257</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="17" t="s">
         <v>1258</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="22" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="18" t="s">
         <v>1259</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="J15" s="19" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
         <v>852</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9" t="s">
@@ -19277,178 +19277,178 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="14" t="s">
         <v>1261</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="22" t="s">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="18" t="s">
         <v>1262</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="14" t="s">
         <v>1263</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="17" t="s">
         <v>1264</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="22" t="s">
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="18" t="s">
         <v>1265</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="19" t="s">
         <v>1266</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="17" t="s">
         <v>1267</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="22" t="s">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="18" t="s">
         <v>1268</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="19" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="17" t="s">
         <v>1270</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="22" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="18" t="s">
         <v>1271</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="J22" s="19" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="17" t="s">
         <v>1273</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="22" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="18" t="s">
         <v>1274</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="19" t="s">
         <v>1275</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="17" t="s">
         <v>1276</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="22" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="18" t="s">
         <v>1277</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J24" s="19" t="s">
         <v>1278</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="22" t="s">
         <v>1279</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="22" t="s">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="18" t="s">
         <v>1280</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="19" t="s">
         <v>1281</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="17" t="s">
         <v>1282</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="22" t="s">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="18" t="s">
         <v>1283</v>
       </c>
-      <c r="J26" s="23" t="s">
+      <c r="J26" s="19" t="s">
         <v>1284</v>
       </c>
     </row>
@@ -19481,48 +19481,48 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27" t="s">
+      <c r="D28" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="J28" s="27" t="s">
+      <c r="J28" s="23" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="23" t="s">
         <v>156</v>
       </c>
     </row>
@@ -19531,7 +19531,7 @@
         <v>870</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9" t="s">
@@ -19555,46 +19555,46 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="17" t="s">
         <v>1285</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="22" t="s">
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="18" t="s">
         <v>1286</v>
       </c>
-      <c r="J31" s="23" t="s">
+      <c r="J31" s="19" t="s">
         <v>1287</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="17" t="s">
         <v>1288</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="22" t="s">
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="18" t="s">
         <v>1289</v>
       </c>
-      <c r="J32" s="23" t="s">
+      <c r="J32" s="19" t="s">
         <v>1290</v>
       </c>
     </row>
@@ -19602,167 +19602,167 @@
       <c r="A33" t="s">
         <v>1291</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="18"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>1292</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C34" t="s">
         <v>1291</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="18"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>1293</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>1291</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="18"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>1294</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C36" t="s">
         <v>1291</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="18"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>1295</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="18"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>1296</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>1295</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="18"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>1297</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C39" t="s">
         <v>1295</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="18"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27" t="s">
+      <c r="C40" s="23"/>
+      <c r="D40" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27" t="s">
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23" t="s">
         <v>1299</v>
       </c>
-      <c r="J40" s="27" t="s">
+      <c r="J40" s="23" t="s">
         <v>1300</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="23" t="s">
         <v>874</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27" t="s">
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23" t="s">
         <v>875</v>
       </c>
-      <c r="J41" s="27" t="s">
+      <c r="J41" s="23" t="s">
         <v>876</v>
       </c>
     </row>
@@ -19815,50 +19815,50 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="24" t="s">
         <v>1307</v>
       </c>
-      <c r="B44" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="28" t="s">
+      <c r="B44" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>874</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28" t="s">
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24" t="s">
         <v>1308</v>
       </c>
-      <c r="J44" s="28" t="s">
+      <c r="J44" s="24" t="s">
         <v>1309</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="25" t="s">
         <v>1310</v>
       </c>
-      <c r="B45" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="29" t="s">
+      <c r="B45" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="25" t="s">
         <v>874</v>
       </c>
-      <c r="D45" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29" t="s">
+      <c r="D45" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25" t="s">
         <v>1311</v>
       </c>
-      <c r="J45" s="29" t="s">
+      <c r="J45" s="25" t="s">
         <v>1312</v>
       </c>
     </row>
@@ -19869,13 +19869,13 @@
       <c r="B46" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="24" t="s">
         <v>1307</v>
       </c>
-      <c r="I46" s="19" t="s">
+      <c r="I46" s="15" t="s">
         <v>1314</v>
       </c>
-      <c r="J46" s="20" t="s">
+      <c r="J46" s="16" t="s">
         <v>1315</v>
       </c>
     </row>
@@ -19886,7 +19886,7 @@
       <c r="B47" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="24" t="s">
         <v>1307</v>
       </c>
     </row>
@@ -19897,58 +19897,58 @@
       <c r="B48" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="24" t="s">
         <v>874</v>
       </c>
       <c r="D48" t="s">
         <v>51</v>
       </c>
-      <c r="I48" s="30" t="s">
+      <c r="I48" s="26" t="s">
         <v>1318</v>
       </c>
-      <c r="J48" s="31" t="s">
+      <c r="J48" s="27" t="s">
         <v>1319</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27" t="s">
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23" t="s">
         <v>878</v>
       </c>
-      <c r="J49" s="27" t="s">
+      <c r="J49" s="23" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="25" t="s">
         <v>1320</v>
       </c>
-      <c r="B50" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="29" t="s">
+      <c r="B50" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
       <c r="I50" t="s">
         <v>1321</v>
       </c>
@@ -19957,42 +19957,42 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="25" t="s">
         <v>1323</v>
       </c>
-      <c r="B51" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="29" t="s">
+      <c r="B51" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D51" s="29" t="s">
+      <c r="D51" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="25" t="s">
         <v>1324</v>
       </c>
-      <c r="B52" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="29" t="s">
+      <c r="B52" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
       <c r="I52" t="s">
         <v>1325</v>
       </c>
@@ -20001,124 +20001,124 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="25" t="s">
         <v>1327</v>
       </c>
-      <c r="B53" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="29" t="s">
+      <c r="B53" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D53" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
+      <c r="D53" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27" t="s">
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23" t="s">
         <v>881</v>
       </c>
-      <c r="J54" s="27" t="s">
+      <c r="J54" s="23" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="25" t="s">
         <v>1328</v>
       </c>
-      <c r="B55" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="27" t="s">
+      <c r="B55" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="25" t="s">
         <v>1329</v>
       </c>
-      <c r="B56" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="27" t="s">
+      <c r="B56" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="25" t="s">
         <v>1330</v>
       </c>
-      <c r="B57" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="27" t="s">
+      <c r="B57" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="25" t="s">
         <v>1331</v>
       </c>
-      <c r="B58" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="27" t="s">
+      <c r="B58" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
       <c r="I58" t="s">
         <v>1332</v>
       </c>
@@ -20127,24 +20127,24 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="23" t="s">
         <v>883</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27" t="s">
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23" t="s">
         <v>884</v>
       </c>
-      <c r="J59" s="27" t="s">
+      <c r="J59" s="23" t="s">
         <v>885</v>
       </c>
     </row>
@@ -20152,39 +20152,39 @@
       <c r="A60" t="s">
         <v>1334</v>
       </c>
-      <c r="B60" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="29" t="s">
+      <c r="B60" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="25" t="s">
         <v>883</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>1335</v>
       </c>
-      <c r="B61" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="29" t="s">
+      <c r="B61" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>883</v>
       </c>
-      <c r="D61" s="29" t="s">
+      <c r="D61" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
       <c r="I61" t="s">
         <v>1336</v>
       </c>
@@ -20196,19 +20196,19 @@
       <c r="A62" t="s">
         <v>1338</v>
       </c>
-      <c r="B62" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="29" t="s">
+      <c r="B62" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="25" t="s">
         <v>883</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
       <c r="I62" t="s">
         <v>1339</v>
       </c>
@@ -20217,44 +20217,44 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27" t="s">
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23" t="s">
         <v>887</v>
       </c>
-      <c r="J63" s="27" t="s">
+      <c r="J63" s="23" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="25" t="s">
         <v>1331</v>
       </c>
-      <c r="B64" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="27" t="s">
+      <c r="B64" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
       <c r="I64" t="s">
         <v>1332</v>
       </c>
@@ -20266,143 +20266,143 @@
       <c r="A65" t="s">
         <v>1341</v>
       </c>
-      <c r="B65" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="27" t="s">
+      <c r="B65" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="29"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>1342</v>
       </c>
-      <c r="B66" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="27" t="s">
+      <c r="B66" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
     </row>
     <row r="67" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="23" t="s">
         <v>889</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="C67" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27" t="s">
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23" t="s">
         <v>890</v>
       </c>
-      <c r="J67" s="27" t="s">
+      <c r="J67" s="23" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="25" t="s">
         <v>1343</v>
       </c>
-      <c r="B68" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="27" t="s">
+      <c r="B68" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="23" t="s">
         <v>889</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="25" t="s">
         <v>1344</v>
       </c>
-      <c r="B69" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="27" t="s">
+      <c r="B69" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="23" t="s">
         <v>889</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C70" s="27" t="s">
+      <c r="C70" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27" t="s">
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23" t="s">
         <v>893</v>
       </c>
-      <c r="J70" s="27" t="s">
+      <c r="J70" s="23" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="25" t="s">
         <v>1331</v>
       </c>
-      <c r="B71" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C71" s="27" t="s">
+      <c r="B71" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
       <c r="I71" t="s">
         <v>1332</v>
       </c>
@@ -20411,46 +20411,46 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A72" s="28" t="s">
+      <c r="A72" s="24" t="s">
         <v>1345</v>
       </c>
-      <c r="B72" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="27" t="s">
+      <c r="B72" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D72" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="19" t="s">
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="15" t="s">
         <v>1346</v>
       </c>
-      <c r="J72" s="20" t="s">
+      <c r="J72" s="16" t="s">
         <v>1347</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="24" t="s">
+      <c r="A73" s="20" t="s">
         <v>1348</v>
       </c>
-      <c r="B73" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" s="27" t="s">
+      <c r="B73" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C73" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="D73" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
+      <c r="D73" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
       <c r="I73" t="s">
         <v>1349</v>
       </c>
@@ -20459,48 +20459,48 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A74" s="24" t="s">
+      <c r="A74" s="20" t="s">
         <v>1351</v>
       </c>
-      <c r="B74" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="27" t="s">
+      <c r="B74" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="D74" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
+      <c r="D74" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
       <c r="I74" t="s">
         <v>1352</v>
       </c>
-      <c r="J74" s="18" t="s">
+      <c r="J74" s="14" t="s">
         <v>1353</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A75" s="27" t="s">
+      <c r="A75" s="23" t="s">
         <v>895</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="27" t="s">
+      <c r="C75" s="23" t="s">
         <v>1298</v>
       </c>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27" t="s">
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="23" t="s">
         <v>896</v>
       </c>
-      <c r="J75" s="27" t="s">
+      <c r="J75" s="23" t="s">
         <v>897</v>
       </c>
     </row>
@@ -20589,22 +20589,22 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A79" s="32" t="s">
+      <c r="A79" s="28" t="s">
         <v>1354</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18" t="s">
+      <c r="C79" s="14"/>
+      <c r="D79" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="18"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
@@ -20613,7 +20613,7 @@
       <c r="B80" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C80" s="32" t="s">
+      <c r="C80" s="28" t="s">
         <v>1354</v>
       </c>
       <c r="D80" s="10" t="s">
@@ -20643,7 +20643,7 @@
       <c r="B81" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C81" s="32" t="s">
+      <c r="C81" s="28" t="s">
         <v>1354</v>
       </c>
       <c r="D81" s="10" t="s">
@@ -20663,50 +20663,50 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A82" s="32" t="s">
+      <c r="A82" s="28" t="s">
         <v>1355</v>
       </c>
-      <c r="B82" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C82" s="32" t="s">
+      <c r="B82" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" s="28" t="s">
         <v>1354</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="18"/>
-      <c r="H82" s="18"/>
-      <c r="I82" s="33" t="s">
+      <c r="D82" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="29" t="s">
         <v>1356</v>
       </c>
-      <c r="J82" s="34" t="s">
+      <c r="J82" s="30" t="s">
         <v>1357</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="28" t="s">
         <v>1358</v>
       </c>
-      <c r="B83" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C83" s="32" t="s">
+      <c r="B83" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="28" t="s">
         <v>1354</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="33" t="s">
+      <c r="D83" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="29" t="s">
         <v>1359</v>
       </c>
-      <c r="J83" s="34" t="s">
+      <c r="J83" s="30" t="s">
         <v>1360</v>
       </c>
     </row>
@@ -20717,7 +20717,7 @@
       <c r="B84" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C84" s="32" t="s">
+      <c r="C84" s="28" t="s">
         <v>1354</v>
       </c>
       <c r="D84" s="10" t="s">
@@ -20747,7 +20747,7 @@
       <c r="B85" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C85" s="32" t="s">
+      <c r="C85" s="28" t="s">
         <v>1354</v>
       </c>
       <c r="D85" s="10" t="s">
@@ -20771,190 +20771,190 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A86" s="32" t="s">
+      <c r="A86" s="28" t="s">
         <v>1361</v>
       </c>
-      <c r="B86" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C86" s="32" t="s">
+      <c r="B86" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C86" s="28" t="s">
         <v>1354</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="33" t="s">
+      <c r="D86" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="29" t="s">
         <v>1362</v>
       </c>
-      <c r="J86" s="34" t="s">
+      <c r="J86" s="30" t="s">
         <v>1363</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="13" t="s">
         <v>1364</v>
       </c>
-      <c r="B87" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C87" s="32" t="s">
+      <c r="B87" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="28" t="s">
         <v>1354</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="19" t="s">
+      <c r="D87" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="15" t="s">
         <v>1365</v>
       </c>
-      <c r="J87" s="20" t="s">
+      <c r="J87" s="16" t="s">
         <v>1366</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="13" t="s">
         <v>1367</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18" t="s">
+      <c r="C88" s="14"/>
+      <c r="D88" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="30" t="s">
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="26" t="s">
         <v>1368</v>
       </c>
-      <c r="J88" s="31" t="s">
+      <c r="J88" s="27" t="s">
         <v>1369</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="32" t="s">
+      <c r="A89" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C89" s="32"/>
-      <c r="D89" s="18" t="s">
+      <c r="C89" s="28"/>
+      <c r="D89" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="19" t="s">
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="15" t="s">
         <v>1371</v>
       </c>
-      <c r="J89" s="20" t="s">
+      <c r="J89" s="16" t="s">
         <v>1372</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="32" t="s">
+      <c r="A90" s="28" t="s">
         <v>1373</v>
       </c>
-      <c r="B90" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C90" s="32" t="s">
+      <c r="B90" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="D90" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="19" t="s">
+      <c r="D90" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="15" t="s">
         <v>1374</v>
       </c>
-      <c r="J90" s="20" t="s">
+      <c r="J90" s="16" t="s">
         <v>1375</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A91" s="32" t="s">
+      <c r="A91" s="28" t="s">
         <v>1376</v>
       </c>
-      <c r="B91" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C91" s="32" t="s">
+      <c r="B91" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="D91" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="30" t="s">
+      <c r="D91" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="26" t="s">
         <v>1377</v>
       </c>
-      <c r="J91" s="31" t="s">
+      <c r="J91" s="27" t="s">
         <v>1378</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="32" t="s">
+      <c r="A92" s="28" t="s">
         <v>1379</v>
       </c>
-      <c r="B92" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" s="32" t="s">
+      <c r="B92" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="D92" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
-      <c r="H92" s="18"/>
-      <c r="I92" s="19" t="s">
+      <c r="D92" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="15" t="s">
         <v>1380</v>
       </c>
-      <c r="J92" s="20" t="s">
+      <c r="J92" s="16" t="s">
         <v>1381</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="13" t="s">
         <v>1382</v>
       </c>
-      <c r="B93" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C93" s="32" t="s">
+      <c r="B93" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C93" s="28" t="s">
         <v>1370</v>
       </c>
-      <c r="D93" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="18"/>
-      <c r="I93" s="30" t="s">
+      <c r="D93" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="26" t="s">
         <v>1383</v>
       </c>
-      <c r="J93" s="31" t="s">
+      <c r="J93" s="27" t="s">
         <v>1384</v>
       </c>
     </row>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF89153C-4EBE-4735-8F5C-F160D3CBF39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8E2AAC-8301-4B78-A63A-B68EF555E3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32355" yWindow="345" windowWidth="25170" windowHeight="15000" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32355" yWindow="345" windowWidth="25170" windowHeight="15000" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,8 @@
     <sheet name="CoreMeta4Cat" sheetId="3" r:id="rId3"/>
     <sheet name="Synthesis" sheetId="4" r:id="rId4"/>
     <sheet name="Characterization" sheetId="5" r:id="rId5"/>
-    <sheet name="Reaction_original" sheetId="8" r:id="rId6"/>
-    <sheet name="Reaction" sheetId="6" r:id="rId7"/>
-    <sheet name="Simulation" sheetId="7" r:id="rId8"/>
+    <sheet name="Reaction" sheetId="9" r:id="rId6"/>
+    <sheet name="Simulation" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5044" uniqueCount="1231">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -3891,51 +3890,12 @@
   <si>
     <t>The electrode where oxidation occurs in an electrochemical cell. It is the positive electrode in an electrolytic cell, while it is the negative electrode in a galvanic cell.</t>
   </si>
-  <si>
-    <t>cell operating mode</t>
-  </si>
-  <si>
-    <t>coremeta4cat:cell_operating_mode</t>
-  </si>
-  <si>
-    <t>the functional mode of an electrochemical cell based on the direction of energy conversion, specifying whether the system generates electrical energy from spontaneous reactions or consumes electrical energy to drive non-spontaneous reactions.</t>
-  </si>
-  <si>
-    <t>active area</t>
-  </si>
-  <si>
-    <t>voc4cat:0007258</t>
-  </si>
-  <si>
-    <t>In contrast to substrate area, the actual area of a sample or electrode which is active.</t>
-  </si>
-  <si>
-    <t>galvanic cell</t>
-  </si>
-  <si>
-    <t>voc4cat:0007256</t>
-  </si>
-  <si>
-    <t>An electrochemical cell that converts chemical energy into electrical energy. A cell in which chemical reactions occur spontaneously at the electrodes when they are connected through an external circuit, producing an electrical current.</t>
-  </si>
-  <si>
-    <t>electrolytic cell</t>
-  </si>
-  <si>
-    <t>faradaic current</t>
-  </si>
-  <si>
-    <t>voc4cat:0007259</t>
-  </si>
-  <si>
-    <t>The current that is flowing through an electrochemical cell and is causing (or is caused by) chemical reactions (charge transfer) occurring at the electrode surfaces.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3966,28 +3926,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4039,26 +3979,8 @@
         <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor theme="4" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -4107,67 +4029,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -4221,35 +4087,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18323,8 +18160,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4241D815-8C04-4064-89DE-57B4438C4484}">
-  <dimension ref="A1:J31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118C8BAC-9B70-4E7A-BFF0-9A2BB55A4E4D}">
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -18880,857 +18717,51 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="A22" s="16" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="s">
-        <v>884</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>885</v>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>1227</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>886</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D23" s="11" t="s">
+      <c r="A23" s="16" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11" t="s">
-        <v>887</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11" t="s">
-        <v>890</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>892</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11" t="s">
-        <v>893</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11" t="s">
-        <v>896</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>898</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11" t="s">
-        <v>899</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>901</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11" t="s">
-        <v>902</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10" t="s">
-        <v>905</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>907</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>908</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>910</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10" t="s">
-        <v>911</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="46" customWidth="1"/>
-    <col min="10" max="10" width="196.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9" t="s">
-        <v>853</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>855</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
-        <v>856</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>865</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>867</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
-        <v>868</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>871</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>871</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>875</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="145" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11" t="s">
-        <v>878</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>876</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>880</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>880</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17" t="s">
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17" t="s">
         <v>1229</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J23" s="18" t="s">
         <v>1230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>880</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23" t="s">
-        <v>1235</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="27" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="31"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="25" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>880</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="27" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -19987,17 +19018,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I17" r:id="rId1" xr:uid="{9B084770-82E4-4C2F-BB73-1026CC166C8F}"/>
-    <hyperlink ref="I18" r:id="rId2" xr:uid="{84C1E994-9822-4DA4-82EC-77E0C3A22C65}"/>
-    <hyperlink ref="I20" r:id="rId3" xr:uid="{D271BD98-633B-40A5-ABD8-541E13FCDE87}"/>
-    <hyperlink ref="I21" r:id="rId4" xr:uid="{9760039F-55FD-4E49-9DCC-DAB8F932008D}"/>
-    <hyperlink ref="I23" r:id="rId5" xr:uid="{ED8919F5-CC95-46F6-BF2C-F21A73C799E4}"/>
+    <hyperlink ref="I22" r:id="rId1" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
+    <hyperlink ref="I23" r:id="rId2" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
